--- a/development/one_file_rosetta_output/SP112959_rosetta.xlsx
+++ b/development/one_file_rosetta_output/SP112959_rosetta.xlsx
@@ -398,14 +398,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
     <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
     <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -426,10 +427,15 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>N indels</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>Example n</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Indel in context</t>
         </is>
@@ -452,9 +458,12 @@
         </is>
       </c>
       <c r="D2" s="4">
+        <v>2</v>
+      </c>
+      <c r="E2" s="4">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -510,7 +519,10 @@
       <c r="D3" s="4">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="4">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -538,7 +550,10 @@
       <c r="D4" s="4">
         <v>1</v>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -609,7 +624,10 @@
       <c r="D5" s="4">
         <v>1</v>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="4">
+        <v>1</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -672,7 +690,10 @@
       <c r="D6" s="4">
         <v>1</v>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -700,7 +721,10 @@
       <c r="D7" s="4">
         <v>1</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -786,7 +810,10 @@
       <c r="D8" s="4">
         <v>1</v>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="4">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -814,7 +841,10 @@
       <c r="D9" s="4">
         <v>1</v>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="4">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -877,7 +907,10 @@
       <c r="D10" s="4">
         <v>1</v>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="4">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -905,7 +938,10 @@
       <c r="D11" s="4">
         <v>1</v>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="4">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1028,7 +1064,10 @@
       <c r="D12" s="4">
         <v>1</v>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="4">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1149,9 +1188,12 @@
         </is>
       </c>
       <c r="D13" s="4">
+        <v>2</v>
+      </c>
+      <c r="E13" s="4">
         <v>1</v>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1207,7 +1249,10 @@
       <c r="D14" s="4">
         <v>2</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="4">
+        <v>2</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1263,7 +1308,10 @@
       <c r="D15" s="4">
         <v>1</v>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="4">
+        <v>1</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1324,9 +1372,12 @@
         </is>
       </c>
       <c r="D16" s="4">
+        <v>20</v>
+      </c>
+      <c r="E16" s="4">
         <v>1</v>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1425,9 +1476,12 @@
         </is>
       </c>
       <c r="D17" s="4">
+        <v>20</v>
+      </c>
+      <c r="E17" s="4">
         <v>2</v>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1526,9 +1580,12 @@
         </is>
       </c>
       <c r="D18" s="4">
+        <v>20</v>
+      </c>
+      <c r="E18" s="4">
         <v>3</v>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1619,9 +1676,12 @@
         </is>
       </c>
       <c r="D19" s="4">
+        <v>20</v>
+      </c>
+      <c r="E19" s="4">
         <v>4</v>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1720,9 +1780,12 @@
         </is>
       </c>
       <c r="D20" s="4">
+        <v>20</v>
+      </c>
+      <c r="E20" s="4">
         <v>5</v>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1813,9 +1876,12 @@
         </is>
       </c>
       <c r="D21" s="4">
+        <v>20</v>
+      </c>
+      <c r="E21" s="4">
         <v>6</v>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1914,9 +1980,12 @@
         </is>
       </c>
       <c r="D22" s="4">
+        <v>20</v>
+      </c>
+      <c r="E22" s="4">
         <v>7</v>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2067,9 +2136,12 @@
         </is>
       </c>
       <c r="D23" s="4">
+        <v>20</v>
+      </c>
+      <c r="E23" s="4">
         <v>8</v>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2228,9 +2300,12 @@
         </is>
       </c>
       <c r="D24" s="4">
+        <v>20</v>
+      </c>
+      <c r="E24" s="4">
         <v>9</v>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2396,9 +2471,12 @@
         </is>
       </c>
       <c r="D25" s="4">
+        <v>20</v>
+      </c>
+      <c r="E25" s="4">
         <v>10</v>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2497,9 +2575,12 @@
         </is>
       </c>
       <c r="D26" s="4">
+        <v>20</v>
+      </c>
+      <c r="E26" s="4">
         <v>11</v>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2598,9 +2679,12 @@
         </is>
       </c>
       <c r="D27" s="4">
+        <v>20</v>
+      </c>
+      <c r="E27" s="4">
         <v>12</v>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2699,9 +2783,12 @@
         </is>
       </c>
       <c r="D28" s="4">
+        <v>20</v>
+      </c>
+      <c r="E28" s="4">
         <v>13</v>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2875,9 +2962,12 @@
         </is>
       </c>
       <c r="D29" s="4">
+        <v>20</v>
+      </c>
+      <c r="E29" s="4">
         <v>14</v>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2976,9 +3066,12 @@
         </is>
       </c>
       <c r="D30" s="4">
+        <v>20</v>
+      </c>
+      <c r="E30" s="4">
         <v>15</v>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3069,9 +3162,12 @@
         </is>
       </c>
       <c r="D31" s="4">
+        <v>20</v>
+      </c>
+      <c r="E31" s="4">
         <v>16</v>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3170,9 +3266,12 @@
         </is>
       </c>
       <c r="D32" s="4">
+        <v>20</v>
+      </c>
+      <c r="E32" s="4">
         <v>17</v>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3278,9 +3377,12 @@
         </is>
       </c>
       <c r="D33" s="4">
+        <v>20</v>
+      </c>
+      <c r="E33" s="4">
         <v>18</v>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3416,9 +3518,12 @@
         </is>
       </c>
       <c r="D34" s="4">
+        <v>20</v>
+      </c>
+      <c r="E34" s="4">
         <v>19</v>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3541,7 +3646,10 @@
       <c r="D35" s="4">
         <v>20</v>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E35" s="4">
+        <v>20</v>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3672,7 +3780,10 @@
       <c r="D36" s="4">
         <v>1</v>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E36" s="4">
+        <v>1</v>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3741,9 +3852,12 @@
         </is>
       </c>
       <c r="D37" s="4">
+        <v>11</v>
+      </c>
+      <c r="E37" s="4">
         <v>1</v>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3842,9 +3956,12 @@
         </is>
       </c>
       <c r="D38" s="4">
+        <v>11</v>
+      </c>
+      <c r="E38" s="4">
         <v>2</v>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3935,9 +4052,12 @@
         </is>
       </c>
       <c r="D39" s="4">
+        <v>11</v>
+      </c>
+      <c r="E39" s="4">
         <v>3</v>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4021,9 +4141,12 @@
         </is>
       </c>
       <c r="D40" s="4">
+        <v>11</v>
+      </c>
+      <c r="E40" s="4">
         <v>4</v>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4114,9 +4237,12 @@
         </is>
       </c>
       <c r="D41" s="4">
+        <v>11</v>
+      </c>
+      <c r="E41" s="4">
         <v>5</v>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4200,9 +4326,12 @@
         </is>
       </c>
       <c r="D42" s="4">
+        <v>11</v>
+      </c>
+      <c r="E42" s="4">
         <v>6</v>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4286,9 +4415,12 @@
         </is>
       </c>
       <c r="D43" s="4">
+        <v>11</v>
+      </c>
+      <c r="E43" s="4">
         <v>7</v>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4379,9 +4511,12 @@
         </is>
       </c>
       <c r="D44" s="4">
+        <v>11</v>
+      </c>
+      <c r="E44" s="4">
         <v>8</v>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4472,9 +4607,12 @@
         </is>
       </c>
       <c r="D45" s="4">
+        <v>11</v>
+      </c>
+      <c r="E45" s="4">
         <v>9</v>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4565,9 +4703,12 @@
         </is>
       </c>
       <c r="D46" s="4">
+        <v>11</v>
+      </c>
+      <c r="E46" s="4">
         <v>10</v>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4660,7 +4801,10 @@
       <c r="D47" s="4">
         <v>11</v>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="E47" s="4">
+        <v>11</v>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4751,9 +4895,12 @@
         </is>
       </c>
       <c r="D48" s="4">
+        <v>3</v>
+      </c>
+      <c r="E48" s="4">
         <v>1</v>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4859,9 +5006,12 @@
         </is>
       </c>
       <c r="D49" s="4">
+        <v>3</v>
+      </c>
+      <c r="E49" s="4">
         <v>2</v>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4977,7 +5127,10 @@
       <c r="D50" s="4">
         <v>3</v>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E50" s="4">
+        <v>3</v>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5108,7 +5261,10 @@
       <c r="D51" s="4">
         <v>1</v>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E51" s="4">
+        <v>1</v>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5171,7 +5327,10 @@
       <c r="D52" s="4">
         <v>1</v>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="E52" s="4">
+        <v>1</v>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5272,7 +5431,10 @@
       <c r="D53" s="4">
         <v>1</v>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E53" s="4">
+        <v>1</v>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5342,9 +5504,12 @@
         </is>
       </c>
       <c r="D54" s="4">
+        <v>2</v>
+      </c>
+      <c r="E54" s="4">
         <v>1</v>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5416,7 +5581,10 @@
       <c r="D55" s="4">
         <v>2</v>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E55" s="4">
+        <v>2</v>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5488,7 +5656,10 @@
       <c r="D56" s="4">
         <v>1</v>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="E56" s="4">
+        <v>1</v>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5560,7 +5731,10 @@
       <c r="D57" s="4">
         <v>1</v>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E57" s="4">
+        <v>1</v>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5614,22 +5788,27 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="20">
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
     <mergeCell ref="A16:A35"/>
     <mergeCell ref="B16:B35"/>
     <mergeCell ref="C16:C35"/>
+    <mergeCell ref="D16:D35"/>
     <mergeCell ref="A37:A47"/>
     <mergeCell ref="B37:B47"/>
     <mergeCell ref="C37:C47"/>
+    <mergeCell ref="D37:D47"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="B48:B50"/>
     <mergeCell ref="C48:C50"/>
+    <mergeCell ref="D48:D50"/>
     <mergeCell ref="A54:A55"/>
     <mergeCell ref="B54:B55"/>
     <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/development/one_file_rosetta_output/SP112959_rosetta.xlsx
+++ b/development/one_file_rosetta_output/SP112959_rosetta.xlsx
@@ -444,21 +444,21 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>A[Del(C):R1]A</t>
+          <t>Del2:U2:R(5,)</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>[Del(C):R1]A</t>
+          <t>Del(2,):U(1,2):R(5,)</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>DEL:C:1:0</t>
+          <t>DEL:repeats:2:5+</t>
         </is>
       </c>
       <c r="D2" s="4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E2" s="4">
         <v>1</v>
@@ -469,7 +469,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TCTGA</t>
+            <t>GCCAT</t>
           </r>
           <r>
             <rPr>
@@ -483,7 +483,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>C</t>
+            <t>TC</t>
           </r>
           <r>
             <rPr>
@@ -493,9 +493,54 @@
           </r>
           <r>
             <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAAGCCAGAAAATAAGGGAA</t>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TC</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TC</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TC</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TC</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TC</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TC</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TTTCATGAACCAACAGCAGG</t>
           </r>
         </is>
       </c>
@@ -503,30 +548,103 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>A[Del(C):R2]T</t>
+          <t>Del2:U2:R(5,)</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>[Del(C):R2]T</t>
+          <t>Del(2,):U(1,2):R(5,)</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t/>
+          <t>DEL:repeats:2:5+</t>
         </is>
       </c>
       <c r="D3" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E3" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
           <r>
-            <rPr/>
-            <t/>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CTTTG</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>&lt;</t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CCTGCCACCATGAAAGACTG</t>
           </r>
         </is>
       </c>
@@ -534,24 +652,24 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>T[Del(C):R3]A</t>
+          <t>Del2:U2:R(5,)</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>[Del(C):R3]A</t>
+          <t>Del(2,):U(1,2):R(5,)</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>DEL:C:1:2</t>
+          <t>DEL:repeats:2:5+</t>
         </is>
       </c>
       <c r="D4" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E4" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
@@ -559,7 +677,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>GTTCT</t>
+            <t>GCCAA</t>
           </r>
           <r>
             <rPr>
@@ -573,7 +691,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>C</t>
+            <t>AG</t>
           </r>
           <r>
             <rPr>
@@ -586,21 +704,43 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>C</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>C</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAAATTCAGTACTTCTGGC</t>
+            <t>AG</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AG</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AG</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AG</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AG</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AAAGAGAGAGAAAGAGTACT</t>
           </r>
         </is>
       </c>
@@ -608,24 +748,24 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>A[Del(T):R2]C</t>
+          <t>Del2:U2:R(5,)</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>A[Del(T):R(1,4)]C</t>
+          <t>Del(2,):U(1,2):R(5,)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>DEL:T:1:1</t>
+          <t>DEL:repeats:2:5+</t>
         </is>
       </c>
       <c r="D5" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E5" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
@@ -633,7 +773,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TATGA</t>
+            <t>TTTAA</t>
           </r>
           <r>
             <rPr>
@@ -647,7 +787,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>T</t>
+            <t>AT</t>
           </r>
           <r>
             <rPr>
@@ -660,13 +800,51 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>CTACACCTAGAAAACCCCAT</t>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CTTATTTCTGATCTTTGCTT</t>
           </r>
         </is>
       </c>
@@ -674,30 +852,95 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>A[Del(T):R4]G</t>
+          <t>Del2:U2:R(5,)</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>A[Del(T):R(1,4)]G</t>
+          <t>Del(2,):U(1,2):R(5,)</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t/>
+          <t>DEL:repeats:2:5+</t>
         </is>
       </c>
       <c r="D6" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E6" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
           <r>
-            <rPr/>
-            <t/>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TAACA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>&lt;</t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CTTTAAGCAGAGAGAGTGAG</t>
           </r>
         </is>
       </c>
@@ -705,24 +948,24 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>A[Del(T):R5]A</t>
+          <t>Del2:U2:R(5,)</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>A[Del(T):R(5,7)]A</t>
+          <t>Del(2,):U(1,2):R(5,)</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>DEL:T:1:4</t>
+          <t>DEL:repeats:2:5+</t>
         </is>
       </c>
       <c r="D7" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E7" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
@@ -730,7 +973,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>ATTTA</t>
+            <t>ACAGG</t>
           </r>
           <r>
             <rPr>
@@ -744,7 +987,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>T</t>
+            <t>TA</t>
           </r>
           <r>
             <rPr>
@@ -757,36 +1000,51 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AGAGGTAAAAAATTCTT</t>
+            <t>TA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TA</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TA</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GACACGTGTGTGTGTGTGTG</t>
           </r>
         </is>
       </c>
@@ -794,30 +1052,155 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>C[Del(T):R3]C</t>
+          <t>Del2:U2:R(5,)</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>C[Del(T):R(1,4)]C</t>
+          <t>Del(2,):U(1,2):R(5,)</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t/>
+          <t>DEL:repeats:2:5+</t>
         </is>
       </c>
       <c r="D8" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E8" s="4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
           <r>
-            <rPr/>
-            <t/>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CCATT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>&lt;</t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TCATACACTTTCCA</t>
           </r>
         </is>
       </c>
@@ -825,24 +1208,24 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>G[Del(T):R2]A</t>
+          <t>Del2:U2:R(5,)</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>G[Del(T):R(1,4)]A</t>
+          <t>Del(2,):U(1,2):R(5,)</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>DEL:T:1:1</t>
+          <t>DEL:repeats:2:5+</t>
         </is>
       </c>
       <c r="D9" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E9" s="4">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -850,7 +1233,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>CACAG</t>
+            <t>GTGGC</t>
           </r>
           <r>
             <rPr>
@@ -864,7 +1247,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>T</t>
+            <t>GA</t>
           </r>
           <r>
             <rPr>
@@ -877,13 +1260,111 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AGGACAGGCTATTGGGGTTC</t>
+            <t>GA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GA</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GA</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GA</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GA</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GA</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GA</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AACAGAGAGAAT</t>
           </r>
         </is>
       </c>
@@ -891,30 +1372,170 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>G[Del(T):R2]C</t>
+          <t>Del2:U2:R(5,)</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>G[Del(T):R(1,4)]C</t>
+          <t>Del(2,):U(1,2):R(5,)</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t/>
+          <t>DEL:repeats:2:5+</t>
         </is>
       </c>
       <c r="D10" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E10" s="4">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
           <r>
-            <rPr/>
-            <t/>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TAATA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>&lt;</t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TG</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TG</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TG</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TG</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TG</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TG</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TG</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TG</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TG</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TG</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TG</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TG</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TG</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TG</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TG</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TG</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TATAAACCAT</t>
           </r>
         </is>
       </c>
@@ -922,24 +1543,24 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>A[Ins(T):R(9,)]C</t>
+          <t>Del2:U2:R(5,)</t>
         </is>
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>A[Ins(T):R(8,)]C</t>
+          <t>Del(2,):U(1,2):R(5,)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>INS:T:1:5+</t>
+          <t>DEL:repeats:2:5+</t>
         </is>
       </c>
       <c r="D11" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E11" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -947,7 +1568,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TTTTA</t>
+            <t>ATTAA</t>
           </r>
           <r>
             <rPr>
@@ -961,7 +1582,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>T</t>
+            <t>TC</t>
           </r>
           <r>
             <rPr>
@@ -974,73 +1595,51 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>CTTGCCTAACTG</t>
+            <t>TC</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TC</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TC</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TC</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TC</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TC</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TTCTTACTTGCTCACTCTGA</t>
           </r>
         </is>
       </c>
@@ -1048,24 +1647,24 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>C[Ins(T):R(9,)]G</t>
+          <t>Del2:U2:R(5,)</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>C[Ins(T):R(8,)]G</t>
+          <t>Del(2,):U(1,2):R(5,)</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>INS:T:1:5+</t>
+          <t>DEL:repeats:2:5+</t>
         </is>
       </c>
       <c r="D12" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E12" s="4">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -1073,7 +1672,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TTGGC</t>
+            <t>GAGAA</t>
           </r>
           <r>
             <rPr>
@@ -1087,7 +1686,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>T</t>
+            <t>AG</t>
           </r>
           <r>
             <rPr>
@@ -1100,73 +1699,51 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GGAGACGGAGTT</t>
+            <t>AG</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AG</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AG</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AG</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AG</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AG</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GAGGAGGAGGAGGATTGAGA</t>
           </r>
         </is>
       </c>
@@ -1174,24 +1751,24 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Del(10,):U1:R1</t>
+          <t>Del2:U2:R(5,)</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>Del(5,):R1</t>
+          <t>Del(2,):U(1,2):R(5,)</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:5+:0</t>
+          <t>DEL:repeats:2:5+</t>
         </is>
       </c>
       <c r="D13" s="4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E13" s="4">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -1199,7 +1776,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TTTTG</t>
+            <t>AAAAA</t>
           </r>
           <r>
             <rPr>
@@ -1213,7 +1790,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AAAACTTTTTTCT</t>
+            <t>AT</t>
           </r>
           <r>
             <rPr>
@@ -1223,9 +1800,54 @@
           </r>
           <r>
             <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TCCCAGTACGTAGAGAAATC</t>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TGACCAGTGAAGACAAATTC</t>
           </r>
         </is>
       </c>
@@ -1233,24 +1855,24 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Del(10,):U1:R1</t>
+          <t>Del2:U2:R(5,)</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>Del(5,):R1</t>
+          <t>Del(2,):U(1,2):R(5,)</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:5+:0</t>
+          <t>DEL:repeats:2:5+</t>
         </is>
       </c>
       <c r="D14" s="4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E14" s="4">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -1258,7 +1880,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TTTTT</t>
+            <t>CACAT</t>
           </r>
           <r>
             <rPr>
@@ -1272,7 +1894,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>CCTTTCAAAG</t>
+            <t>AC</t>
           </r>
           <r>
             <rPr>
@@ -1282,9 +1904,129 @@
           </r>
           <r>
             <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AATATGCTTCCTACATGCTG</t>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AGACACAC</t>
           </r>
         </is>
       </c>
@@ -1292,24 +2034,24 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Del2:U2:R2</t>
+          <t>Del2:U2:R(5,)</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>Del(2,8):U(1,2):R(2,4)</t>
+          <t>Del(2,):U(1,2):R(5,)</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:2:1</t>
+          <t>DEL:repeats:2:5+</t>
         </is>
       </c>
       <c r="D15" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E15" s="4">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
@@ -1317,7 +2059,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TGTAA</t>
+            <t>ATTGT</t>
           </r>
           <r>
             <rPr>
@@ -1331,7 +2073,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AC</t>
+            <t>TC</t>
           </r>
           <r>
             <rPr>
@@ -1344,13 +2086,51 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AGTCAAAAGAGATTAAGTAT</t>
+            <t>TC</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TC</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TC</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TC</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TC</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TC</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TTCTCTCTTCTCTCTTTCTG</t>
           </r>
         </is>
       </c>
@@ -1375,7 +2155,7 @@
         <v>20</v>
       </c>
       <c r="E16" s="4">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
@@ -1383,7 +2163,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>GCCAT</t>
+            <t>GATAA</t>
           </r>
           <r>
             <rPr>
@@ -1397,7 +2177,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TC</t>
+            <t>AG</t>
           </r>
           <r>
             <rPr>
@@ -1410,51 +2190,43 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TC</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TC</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TC</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TC</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TC</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TC</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TTTCATGAACCAACAGCAGG</t>
+            <t>AG</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AG</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AG</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AG</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AG</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GGGAGAAGTGCTACACACTT</t>
           </r>
         </is>
       </c>
@@ -1479,7 +2251,7 @@
         <v>20</v>
       </c>
       <c r="E17" s="4">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
@@ -1487,7 +2259,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>CTTTG</t>
+            <t>TAGAG</t>
           </r>
           <r>
             <rPr>
@@ -1501,7 +2273,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>CT</t>
+            <t>AT</t>
           </r>
           <r>
             <rPr>
@@ -1514,51 +2286,51 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>CT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>CT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>CT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>CT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>CT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>CT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>CCTGCCACCATGAAAGACTG</t>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GTGTGTGTGTGTGTGTATGT</t>
           </r>
         </is>
       </c>
@@ -1583,7 +2355,7 @@
         <v>20</v>
       </c>
       <c r="E18" s="4">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
@@ -1591,7 +2363,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>GCCAA</t>
+            <t>GAGAA</t>
           </r>
           <r>
             <rPr>
@@ -1652,9 +2424,24 @@
           </r>
           <r>
             <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAAGAGAGAGAAAGAGTACT</t>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AG</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AG</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>ACAGTAGCGTGTCTGGGTCA</t>
           </r>
         </is>
       </c>
@@ -1679,7 +2466,7 @@
         <v>20</v>
       </c>
       <c r="E19" s="4">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
@@ -1687,7 +2474,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TTTAA</t>
+            <t>TTCCA</t>
           </r>
           <r>
             <rPr>
@@ -1756,9 +2543,46 @@
           </r>
           <r>
             <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>CTTATTTCTGATCTTTGCTT</t>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TATAATACACATACACAG</t>
           </r>
         </is>
       </c>
@@ -1783,7 +2607,7 @@
         <v>20</v>
       </c>
       <c r="E20" s="4">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
@@ -1791,7 +2615,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TAACA</t>
+            <t>CCTGC</t>
           </r>
           <r>
             <rPr>
@@ -1805,7 +2629,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>GT</t>
+            <t>AG</t>
           </r>
           <r>
             <rPr>
@@ -1818,43 +2642,73 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>GT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>CTTTAAGCAGAGAGAGTGAG</t>
+            <t>AG</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AG</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AG</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AG</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AG</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AG</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AG</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AG</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AG</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>ACAGAAAGAAAGAAGAAGAG</t>
           </r>
         </is>
       </c>
@@ -1879,7 +2733,7 @@
         <v>20</v>
       </c>
       <c r="E21" s="4">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
@@ -1887,7 +2741,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>ACAGG</t>
+            <t>TAGGA</t>
           </r>
           <r>
             <rPr>
@@ -1901,7 +2755,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TA</t>
+            <t>AT</t>
           </r>
           <r>
             <rPr>
@@ -1914,51 +2768,81 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TA</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TA</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TA</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GACACGTGTGTGTGTGTGTG</t>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GTATGTATATTCTCTCTCTA</t>
           </r>
         </is>
       </c>
@@ -1966,24 +2850,24 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Del2:U2:R(5,)</t>
+          <t>Del3:U3:R(5,)</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>Del(2,):U(1,2):R(5,)</t>
+          <t>Del(3,):U(3,):R(3,)</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:2:5+</t>
+          <t>DEL:repeats:3:4; DEL:repeats:3:5+</t>
         </is>
       </c>
       <c r="D22" s="4">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E22" s="4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
@@ -1991,7 +2875,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>CCATT</t>
+            <t>TATTC</t>
           </r>
           <r>
             <rPr>
@@ -2005,7 +2889,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AC</t>
+            <t>ATT</t>
           </r>
           <r>
             <rPr>
@@ -2018,103 +2902,51 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TCATACACTTTCCA</t>
+            <t>ATT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>ATT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>ATT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>ATT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>ATT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>ATT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TGAGACAGAGTCTTGCTCTG</t>
           </r>
         </is>
       </c>
@@ -2122,24 +2954,24 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Del2:U2:R(5,)</t>
+          <t>Del3:U3:R(5,)</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>Del(2,):U(1,2):R(5,)</t>
+          <t>Del(3,):U(3,):R(3,)</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:2:5+</t>
+          <t>DEL:repeats:3:4; DEL:repeats:3:5+</t>
         </is>
       </c>
       <c r="D23" s="4">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E23" s="4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
@@ -2147,7 +2979,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>GTGGC</t>
+            <t>GCCAA</t>
           </r>
           <r>
             <rPr>
@@ -2161,7 +2993,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>GA</t>
+            <t>AAT</t>
           </r>
           <r>
             <rPr>
@@ -2174,111 +3006,43 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>GA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GA</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GA</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GA</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GA</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GA</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GA</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GA</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AACAGAGAGAAT</t>
+            <t>AAT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AAT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AAT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AAT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AAT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AAAATACAACTCCATAGTAT</t>
           </r>
         </is>
       </c>
@@ -2286,24 +3050,24 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Del2:U2:R(5,)</t>
+          <t>Del3:U3:R(5,)</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>Del(2,):U(1,2):R(5,)</t>
+          <t>Del(3,):U(3,):R(3,)</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:2:5+</t>
+          <t>DEL:repeats:3:4; DEL:repeats:3:5+</t>
         </is>
       </c>
       <c r="D24" s="4">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E24" s="4">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
@@ -2311,7 +3075,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TAATA</t>
+            <t>CAAGC</t>
           </r>
           <r>
             <rPr>
@@ -2325,7 +3089,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TG</t>
+            <t>CCT</t>
           </r>
           <r>
             <rPr>
@@ -2338,118 +3102,36 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TG</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TG</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TG</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TG</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TG</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TG</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TG</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TG</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TG</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TG</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TG</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TG</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TG</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TG</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TG</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TATAAACCAT</t>
+            <t>CCT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CCT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CCT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CCT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TCCAATGCAGCTAAGGACCC</t>
           </r>
         </is>
       </c>
@@ -2457,24 +3139,24 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Del2:U2:R(5,)</t>
+          <t>Del3:U3:R(5,)</t>
         </is>
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>Del(2,):U(1,2):R(5,)</t>
+          <t>Del(3,):U(3,):R(3,)</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:2:5+</t>
+          <t>DEL:repeats:3:4; DEL:repeats:3:5+</t>
         </is>
       </c>
       <c r="D25" s="4">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E25" s="4">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
@@ -2482,7 +3164,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>ATTAA</t>
+            <t>CAAAA</t>
           </r>
           <r>
             <rPr>
@@ -2496,7 +3178,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TC</t>
+            <t>AAC</t>
           </r>
           <r>
             <rPr>
@@ -2509,51 +3191,43 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TC</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TC</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TC</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TC</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TC</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TC</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TTCTTACTTGCTCACTCTGA</t>
+            <t>AAC</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AAC</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AAC</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AAC</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AAC</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AAACAGTGAATAGCCCTTCA</t>
           </r>
         </is>
       </c>
@@ -2561,24 +3235,24 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Del2:U2:R(5,)</t>
+          <t>Del3:U3:R(5,)</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>Del(2,):U(1,2):R(5,)</t>
+          <t>Del(3,):U(3,):R(3,)</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:2:5+</t>
+          <t>DEL:repeats:3:4; DEL:repeats:3:5+</t>
         </is>
       </c>
       <c r="D26" s="4">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E26" s="4">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
@@ -2586,7 +3260,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>GAGAA</t>
+            <t>AAGCT</t>
           </r>
           <r>
             <rPr>
@@ -2600,7 +3274,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AG</t>
+            <t>TTA</t>
           </r>
           <r>
             <rPr>
@@ -2613,51 +3287,36 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AG</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AG</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AG</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AG</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AG</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AG</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GAGGAGGAGGAGGATTGAGA</t>
+            <t>TTA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TTA</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TTA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TTA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TATCTGCTATGGTGATCTGT</t>
           </r>
         </is>
       </c>
@@ -2665,24 +3324,24 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Del2:U2:R(5,)</t>
+          <t>Del3:U3:R(5,)</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>Del(2,):U(1,2):R(5,)</t>
+          <t>Del(3,):U(3,):R(3,)</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:2:5+</t>
+          <t>DEL:repeats:3:4; DEL:repeats:3:5+</t>
         </is>
       </c>
       <c r="D27" s="4">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E27" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
@@ -2690,7 +3349,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AAAAA</t>
+            <t>ATTAC</t>
           </r>
           <r>
             <rPr>
@@ -2704,7 +3363,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AT</t>
+            <t>TAT</t>
           </r>
           <r>
             <rPr>
@@ -2717,51 +3376,36 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TGACCAGTGAAGACAAATTC</t>
+            <t>TAT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TAT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TAT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TAT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TTGAGATGGAGTCTCACTCT</t>
           </r>
         </is>
       </c>
@@ -2769,24 +3413,24 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Del2:U2:R(5,)</t>
+          <t>Del3:U3:R(5,)</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>Del(2,):U(1,2):R(5,)</t>
+          <t>Del(3,):U(3,):R(3,)</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:2:5+</t>
+          <t>DEL:repeats:3:4; DEL:repeats:3:5+</t>
         </is>
       </c>
       <c r="D28" s="4">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E28" s="4">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
@@ -2794,7 +3438,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>CACAT</t>
+            <t>TGATG</t>
           </r>
           <r>
             <rPr>
@@ -2808,7 +3452,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AC</t>
+            <t>ATA</t>
           </r>
           <r>
             <rPr>
@@ -2821,126 +3465,43 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AGACACAC</t>
+            <t>ATA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>ATA</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>ATA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>ATA</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>ATA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CCTCTTAGATGTACTAACTT</t>
           </r>
         </is>
       </c>
@@ -2948,24 +3509,24 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Del2:U2:R(5,)</t>
+          <t>Del3:U3:R(5,)</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>Del(2,):U(1,2):R(5,)</t>
+          <t>Del(3,):U(3,):R(3,)</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:2:5+</t>
+          <t>DEL:repeats:3:4; DEL:repeats:3:5+</t>
         </is>
       </c>
       <c r="D29" s="4">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E29" s="4">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
@@ -2973,7 +3534,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>ATTGT</t>
+            <t>TTAAC</t>
           </r>
           <r>
             <rPr>
@@ -2987,7 +3548,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TC</t>
+            <t>AAT</t>
           </r>
           <r>
             <rPr>
@@ -3000,51 +3561,43 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TC</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TC</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TC</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TC</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TC</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TC</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TTCTCTCTTCTCTCTTTCTG</t>
+            <t>AAT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AAT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AAT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AAT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AAT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AGCACAATGACTATTAGTAA</t>
           </r>
         </is>
       </c>
@@ -3052,24 +3605,24 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Del2:U2:R(5,)</t>
+          <t>Del3:U3:R(5,)</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>Del(2,):U(1,2):R(5,)</t>
+          <t>Del(3,):U(3,):R(3,)</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:2:5+</t>
+          <t>DEL:repeats:3:4; DEL:repeats:3:5+</t>
         </is>
       </c>
       <c r="D30" s="4">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E30" s="4">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
@@ -3077,7 +3630,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>GATAA</t>
+            <t>ATGAC</t>
           </r>
           <r>
             <rPr>
@@ -3091,7 +3644,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AG</t>
+            <t>TAT</t>
           </r>
           <r>
             <rPr>
@@ -3104,43 +3657,43 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AG</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AG</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AG</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AG</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AG</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GGGAGAAGTGCTACACACTT</t>
+            <t>TAT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TAT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TAT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TAT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TAT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TTTGAGACAAAGTCTCCCTC</t>
           </r>
         </is>
       </c>
@@ -3148,24 +3701,24 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Del2:U2:R(5,)</t>
+          <t>Del3:U3:R(5,)</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>Del(2,):U(1,2):R(5,)</t>
+          <t>Del(3,):U(3,):R(3,)</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:2:5+</t>
+          <t>DEL:repeats:3:4; DEL:repeats:3:5+</t>
         </is>
       </c>
       <c r="D31" s="4">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E31" s="4">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
@@ -3173,7 +3726,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TAGAG</t>
+            <t>AAAGT</t>
           </r>
           <r>
             <rPr>
@@ -3187,7 +3740,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AT</t>
+            <t>ATA</t>
           </r>
           <r>
             <rPr>
@@ -3200,51 +3753,43 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GTGTGTGTGTGTGTGTATGT</t>
+            <t>ATA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>ATA</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>ATA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>ATA</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>ATA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AAGACAATCACAGAGATTGG</t>
           </r>
         </is>
       </c>
@@ -3252,24 +3797,24 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Del2:U2:R(5,)</t>
+          <t>Del3:U3:R(5,)</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>Del(2,):U(1,2):R(5,)</t>
+          <t>Del(3,):U(3,):R(3,)</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:2:5+</t>
+          <t>DEL:repeats:3:4; DEL:repeats:3:5+</t>
         </is>
       </c>
       <c r="D32" s="4">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E32" s="4">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -3277,7 +3822,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>GAGAA</t>
+            <t>TACGG</t>
           </r>
           <r>
             <rPr>
@@ -3291,7 +3836,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AG</t>
+            <t>TAT</t>
           </r>
           <r>
             <rPr>
@@ -3304,58 +3849,43 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AG</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AG</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AG</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AG</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AG</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AG</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AG</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>ACAGTAGCGTGTCTGGGTCA</t>
+            <t>TAT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TAT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TAT</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TAT</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TAT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TAGGTCTAGTATTCTACTTA</t>
           </r>
         </is>
       </c>
@@ -3363,24 +3893,24 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Del2:U2:R(5,)</t>
+          <t>Ins2:U2:R(5,)</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>Del(2,):U(1,2):R(5,)</t>
+          <t>Ins(2,):R(5,)</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:2:5+</t>
+          <t>INS:repeats:2:5+</t>
         </is>
       </c>
       <c r="D33" s="4">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E33" s="4">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
@@ -3388,7 +3918,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TTCCA</t>
+            <t>TTTTC</t>
           </r>
           <r>
             <rPr>
@@ -3402,7 +3932,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AT</t>
+            <t>TG</t>
           </r>
           <r>
             <rPr>
@@ -3415,88 +3945,58 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TATAATACACATACACAG</t>
+            <t>TG</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TG</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TG</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TG</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TG</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TG</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TG</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>ATAGTTCAATGACTTTTTAT</t>
           </r>
         </is>
       </c>
@@ -3504,24 +4004,24 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Del2:U2:R(5,)</t>
+          <t>Ins2:U2:R(5,)</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>Del(2,):U(1,2):R(5,)</t>
+          <t>Ins(2,):R(5,)</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:2:5+</t>
+          <t>INS:repeats:2:5+</t>
         </is>
       </c>
       <c r="D34" s="4">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E34" s="4">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -3529,7 +4029,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>CCTGC</t>
+            <t>TACAG</t>
           </r>
           <r>
             <rPr>
@@ -3543,7 +4043,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AG</t>
+            <t>TA</t>
           </r>
           <r>
             <rPr>
@@ -3556,73 +4056,66 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AG</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AG</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AG</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AG</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AG</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AG</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AG</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AG</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AG</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>ACAGAAAGAAAGAAGAAGAG</t>
+            <t>TA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TA</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TA</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TA</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TTTTTGATGCACCAACAAGG</t>
           </r>
         </is>
       </c>
@@ -3630,24 +4123,24 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Del2:U2:R(5,)</t>
+          <t>Ins2:U2:R(5,)</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>Del(2,):U(1,2):R(5,)</t>
+          <t>Ins(2,):R(5,)</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:2:5+</t>
+          <t>INS:repeats:2:5+</t>
         </is>
       </c>
       <c r="D35" s="4">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E35" s="4">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
@@ -3655,7 +4148,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TAGGA</t>
+            <t>TATAC</t>
           </r>
           <r>
             <rPr>
@@ -3669,7 +4162,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AT</t>
+            <t>TA</t>
           </r>
           <r>
             <rPr>
@@ -3682,81 +4175,81 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GTATGTATATTCTCTCTCTA</t>
+            <t>TA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TA</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TA</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TA</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TA</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TGAAAAGAAAAACTACCTAT</t>
           </r>
         </is>
       </c>
@@ -3764,21 +4257,21 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Del3:U3:R3</t>
+          <t>A[Del(C):R1]A</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>Del(3,):U(3,):R(3,)</t>
+          <t>[Del(C):R1]A</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:3:2</t>
+          <t>DEL:C:1:0</t>
         </is>
       </c>
       <c r="D36" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" s="4">
         <v>1</v>
@@ -3789,7 +4282,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AGGAG</t>
+            <t>TCTGA</t>
           </r>
           <r>
             <rPr>
@@ -3803,7 +4296,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>ACC</t>
+            <t>C</t>
           </r>
           <r>
             <rPr>
@@ -3813,24 +4306,9 @@
           </r>
           <r>
             <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>ACC</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>ACC</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>ACTTTCACTCTAAATTAGCA</t>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AAAGCCAGAAAATAAGGGAA</t>
           </r>
         </is>
       </c>
@@ -3838,21 +4316,21 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Del3:U3:R(5,)</t>
+          <t>Del(10,):U1:R1</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>Del(3,):U(3,):R(3,)</t>
+          <t>Del(5,):R1</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:3:4; DEL:repeats:3:5+</t>
+          <t>DEL:repeats:5+:0</t>
         </is>
       </c>
       <c r="D37" s="4">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E37" s="4">
         <v>1</v>
@@ -3863,7 +4341,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TATTC</t>
+            <t>TTTTG</t>
           </r>
           <r>
             <rPr>
@@ -3877,7 +4355,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>ATT</t>
+            <t>AAAACTTTTTTCT</t>
           </r>
           <r>
             <rPr>
@@ -3887,54 +4365,9 @@
           </r>
           <r>
             <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>ATT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>ATT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>ATT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>ATT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>ATT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>ATT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TGAGACAGAGTCTTGCTCTG</t>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TCCCAGTACGTAGAGAAATC</t>
           </r>
         </is>
       </c>
@@ -3942,21 +4375,21 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>Del3:U3:R(5,)</t>
+          <t>Del(10,):U1:R1</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>Del(3,):U(3,):R(3,)</t>
+          <t>Del(5,):R1</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:3:4; DEL:repeats:3:5+</t>
+          <t>DEL:repeats:5+:0</t>
         </is>
       </c>
       <c r="D38" s="4">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E38" s="4">
         <v>2</v>
@@ -3967,7 +4400,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>GCCAA</t>
+            <t>TTTTT</t>
           </r>
           <r>
             <rPr>
@@ -3981,7 +4414,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AAT</t>
+            <t>CCTTTCAAAG</t>
           </r>
           <r>
             <rPr>
@@ -3991,46 +4424,9 @@
           </r>
           <r>
             <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAAATACAACTCCATAGTAT</t>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AATATGCTTCCTACATGCTG</t>
           </r>
         </is>
       </c>
@@ -4038,24 +4434,24 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Del3:U3:R(5,)</t>
+          <t>Del3:M2</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>Del(3,):U(3,):R(3,)</t>
+          <t>Del(3,5):M2</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:3:4; DEL:repeats:3:5+</t>
+          <t>DEL:MH:3:2</t>
         </is>
       </c>
       <c r="D39" s="4">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E39" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
@@ -4063,7 +4459,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>CAAGC</t>
+            <t>ATTTC</t>
           </r>
           <r>
             <rPr>
@@ -4074,10 +4470,19 @@
           <r>
             <rPr>
               <b/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>CCT</t>
+              <u val="double"/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>G</t>
           </r>
           <r>
             <rPr>
@@ -4087,39 +4492,16 @@
           </r>
           <r>
             <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>CCT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>CCT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>CCT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>CCT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TCCAATGCAGCTAAGGACCC</t>
+              <u val="double"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AAGTATCAAAACTGTCCACT</t>
           </r>
         </is>
       </c>
@@ -4127,24 +4509,24 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Del3:U3:R(5,)</t>
+          <t>Del3:M2</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>Del(3,):U(3,):R(3,)</t>
+          <t>Del(3,5):M2</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:3:4; DEL:repeats:3:5+</t>
+          <t>DEL:MH:3:2</t>
         </is>
       </c>
       <c r="D40" s="4">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E40" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
@@ -4152,7 +4534,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>CAAAA</t>
+            <t>TCCTC</t>
           </r>
           <r>
             <rPr>
@@ -4163,10 +4545,19 @@
           <r>
             <rPr>
               <b/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAC</t>
+              <u val="double"/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CT</t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
           </r>
           <r>
             <rPr>
@@ -4176,46 +4567,16 @@
           </r>
           <r>
             <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAC</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAC</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAC</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAC</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAC</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAACAGTGAATAGCCCTTCA</t>
+              <u val="double"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AGTTCATTAATTGATCTTGG</t>
           </r>
         </is>
       </c>
@@ -4223,88 +4584,30 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Del3:U3:R(5,)</t>
+          <t>A[Del(C):R2]T</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>Del(3,):U(3,):R(3,)</t>
+          <t>[Del(C):R2]T</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:3:4; DEL:repeats:3:5+</t>
+          <t/>
         </is>
       </c>
       <c r="D41" s="4">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E41" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
           <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAGCT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>&lt;</t>
-          </r>
-          <r>
-            <rPr>
-              <b/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TTA</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>&gt;</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TTA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TTA</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TTA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TTA</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TATCTGCTATGGTGATCTGT</t>
+            <rPr/>
+            <t/>
           </r>
         </is>
       </c>
@@ -4312,24 +4615,24 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>Del3:U3:R(5,)</t>
+          <t>T[Del(C):R3]A</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>Del(3,):U(3,):R(3,)</t>
+          <t>[Del(C):R3]A</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:3:4; DEL:repeats:3:5+</t>
+          <t>DEL:C:1:2</t>
         </is>
       </c>
       <c r="D42" s="4">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E42" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
@@ -4337,7 +4640,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>ATTAC</t>
+            <t>GTTCT</t>
           </r>
           <r>
             <rPr>
@@ -4351,7 +4654,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TAT</t>
+            <t>C</t>
           </r>
           <r>
             <rPr>
@@ -4364,36 +4667,21 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TAT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TAT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TAT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TAT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TTGAGATGGAGTCTCACTCT</t>
+            <t>C</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>C</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AAAATTCAGTACTTCTGGC</t>
           </r>
         </is>
       </c>
@@ -4401,24 +4689,24 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>Del3:U3:R(5,)</t>
+          <t>A[Del(T):R2]C</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>Del(3,):U(3,):R(3,)</t>
+          <t>A[Del(T):R(1,4)]C</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:3:4; DEL:repeats:3:5+</t>
+          <t>DEL:T:1:1</t>
         </is>
       </c>
       <c r="D43" s="4">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E43" s="4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
@@ -4426,7 +4714,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TGATG</t>
+            <t>TATGA</t>
           </r>
           <r>
             <rPr>
@@ -4440,7 +4728,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>ATA</t>
+            <t>T</t>
           </r>
           <r>
             <rPr>
@@ -4453,43 +4741,13 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>ATA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>ATA</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>ATA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>ATA</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>ATA</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>CCTCTTAGATGTACTAACTT</t>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CTACACCTAGAAAACCCCAT</t>
           </r>
         </is>
       </c>
@@ -4497,95 +4755,30 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>Del3:U3:R(5,)</t>
+          <t>A[Del(T):R4]G</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>Del(3,):U(3,):R(3,)</t>
+          <t>A[Del(T):R(1,4)]G</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:3:4; DEL:repeats:3:5+</t>
+          <t/>
         </is>
       </c>
       <c r="D44" s="4">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E44" s="4">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
           <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TTAAC</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>&lt;</t>
-          </r>
-          <r>
-            <rPr>
-              <b/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>&gt;</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AGCACAATGACTATTAGTAA</t>
+            <rPr/>
+            <t/>
           </r>
         </is>
       </c>
@@ -4593,24 +4786,24 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Del3:U3:R(5,)</t>
+          <t>A[Del(T):R5]A</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>Del(3,):U(3,):R(3,)</t>
+          <t>A[Del(T):R(5,7)]A</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:3:4; DEL:repeats:3:5+</t>
+          <t>DEL:T:1:4</t>
         </is>
       </c>
       <c r="D45" s="4">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E45" s="4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
@@ -4618,7 +4811,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>ATGAC</t>
+            <t>ATTTA</t>
           </r>
           <r>
             <rPr>
@@ -4632,7 +4825,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TAT</t>
+            <t>T</t>
           </r>
           <r>
             <rPr>
@@ -4645,43 +4838,36 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TAT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TAT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TAT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TAT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TAT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TTTGAGACAAAGTCTCCCTC</t>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AGAGGTAAAAAATTCTT</t>
           </r>
         </is>
       </c>
@@ -4689,95 +4875,30 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>Del3:U3:R(5,)</t>
+          <t>C[Del(T):R3]C</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>Del(3,):U(3,):R(3,)</t>
+          <t>C[Del(T):R(1,4)]C</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:3:4; DEL:repeats:3:5+</t>
+          <t/>
         </is>
       </c>
       <c r="D46" s="4">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E46" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
           <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAAGT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>&lt;</t>
-          </r>
-          <r>
-            <rPr>
-              <b/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>ATA</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>&gt;</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>ATA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>ATA</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>ATA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>ATA</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>ATA</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAGACAATCACAGAGATTGG</t>
+            <rPr/>
+            <t/>
           </r>
         </is>
       </c>
@@ -4785,24 +4906,24 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Del3:U3:R(5,)</t>
+          <t>G[Del(T):R2]A</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>Del(3,):U(3,):R(3,)</t>
+          <t>G[Del(T):R(1,4)]A</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:3:4; DEL:repeats:3:5+</t>
+          <t>DEL:T:1:1</t>
         </is>
       </c>
       <c r="D47" s="4">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E47" s="4">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
@@ -4810,7 +4931,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TACGG</t>
+            <t>CACAG</t>
           </r>
           <r>
             <rPr>
@@ -4824,7 +4945,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TAT</t>
+            <t>T</t>
           </r>
           <r>
             <rPr>
@@ -4837,43 +4958,13 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TAT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TAT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TAT</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TAT</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TAT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TAGGTCTAGTATTCTACTTA</t>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AGGACAGGCTATTGGGGTTC</t>
           </r>
         </is>
       </c>
@@ -4881,21 +4972,21 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Ins2:U2:R(5,)</t>
+          <t>G[Del(T):R2]C</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>Ins(2,):R(5,)</t>
+          <t>G[Del(T):R(1,4)]C</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>INS:repeats:2:5+</t>
+          <t/>
         </is>
       </c>
       <c r="D48" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E48" s="4">
         <v>1</v>
@@ -4903,88 +4994,8 @@
       <c r="F48" s="6" t="inlineStr">
         <is>
           <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TTTTC</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>&lt;</t>
-          </r>
-          <r>
-            <rPr>
-              <b/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TG</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>&gt;</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TG</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TG</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TG</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TG</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TG</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TG</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TG</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>ATAGTTCAATGACTTTTTAT</t>
+            <rPr/>
+            <t/>
           </r>
         </is>
       </c>
@@ -4992,24 +5003,24 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Ins2:U2:R(5,)</t>
+          <t>A[Ins(T):R(9,)]C</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>Ins(2,):R(5,)</t>
+          <t>A[Ins(T):R(8,)]C</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>INS:repeats:2:5+</t>
+          <t>INS:T:1:5+</t>
         </is>
       </c>
       <c r="D49" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E49" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
@@ -5017,7 +5028,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TACAG</t>
+            <t>TTTTA</t>
           </r>
           <r>
             <rPr>
@@ -5031,7 +5042,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TA</t>
+            <t>T</t>
           </r>
           <r>
             <rPr>
@@ -5044,66 +5055,73 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TA</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TA</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TA</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TA</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TTTTTGATGCACCAACAAGG</t>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CTTGCCTAACTG</t>
           </r>
         </is>
       </c>
@@ -5111,24 +5129,24 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Ins2:U2:R(5,)</t>
+          <t>C[Ins(T):R(9,)]G</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>Ins(2,):R(5,)</t>
+          <t>C[Ins(T):R(8,)]G</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>INS:repeats:2:5+</t>
+          <t>INS:T:1:5+</t>
         </is>
       </c>
       <c r="D50" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E50" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
@@ -5136,7 +5154,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TATAC</t>
+            <t>TTGGC</t>
           </r>
           <r>
             <rPr>
@@ -5150,7 +5168,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TA</t>
+            <t>T</t>
           </r>
           <r>
             <rPr>
@@ -5163,81 +5181,73 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TA</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TA</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TA</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TA</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TA</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>TGAAAAGAAAAACTACCTAT</t>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GGAGACGGAGTT</t>
           </r>
         </is>
       </c>
@@ -5245,17 +5255,17 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>Ins4:U2:R2</t>
+          <t>Del2:U2:R2</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>Ins(2,):R(2,4)</t>
+          <t>Del(2,8):U(1,2):R(2,4)</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>INS:repeats:4:1</t>
+          <t>DEL:repeats:2:1</t>
         </is>
       </c>
       <c r="D51" s="4">
@@ -5270,7 +5280,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>ATGAT</t>
+            <t>TGTAA</t>
           </r>
           <r>
             <rPr>
@@ -5284,7 +5294,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TATA</t>
+            <t>AC</t>
           </r>
           <r>
             <rPr>
@@ -5297,13 +5307,13 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TATA</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>CCACTGTACTCCAGCAGGGG</t>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AGTCAAAAGAGATTAAGTAT</t>
           </r>
         </is>
       </c>
@@ -5311,17 +5321,17 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>Ins(5,):U(3,):R(5,)</t>
+          <t>Del3:U3:R3</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>Ins(2,):R(5,)</t>
+          <t>Del(3,):U(3,):R(3,)</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>INS:repeats:5+:5+</t>
+          <t>DEL:repeats:3:2</t>
         </is>
       </c>
       <c r="D52" s="4">
@@ -5336,7 +5346,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AGAAG</t>
+            <t>AGGAG</t>
           </r>
           <r>
             <rPr>
@@ -5350,7 +5360,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>GAAAGAAA</t>
+            <t>ACC</t>
           </r>
           <r>
             <rPr>
@@ -5363,51 +5373,21 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>GAAAGAAA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GAAAGAAA</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GAAAGAAA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GAAAGAAA</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GAAAGAAA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GAAAGAAA</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GAAAAGAAAGAAAGAAAGAG</t>
+            <t>ACC</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>ACC</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>ACTTTCACTCTAAATTAGCA</t>
           </r>
         </is>
       </c>
@@ -5415,17 +5395,17 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>Del3:M1</t>
+          <t>Ins4:U2:R2</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>Del(2,5):M1</t>
+          <t>Ins(2,):R(2,4)</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>DEL:MH:3:1</t>
+          <t>INS:repeats:4:1</t>
         </is>
       </c>
       <c r="D53" s="4">
@@ -5440,7 +5420,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TAGGT</t>
+            <t>ATGAT</t>
           </r>
           <r>
             <rPr>
@@ -5451,19 +5431,10 @@
           <r>
             <rPr>
               <b/>
-              <u val="double"/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>G</t>
-          </r>
-          <r>
-            <rPr>
-              <b/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GA</t>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TATA</t>
           </r>
           <r>
             <rPr>
@@ -5473,16 +5444,16 @@
           </r>
           <r>
             <rPr>
-              <u val="double"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>G</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAGTTTAAGTCAATGGATTA</t>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TATA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CCACTGTACTCCAGCAGGGG</t>
           </r>
         </is>
       </c>
@@ -5490,21 +5461,21 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>Del3:M2</t>
+          <t>Ins(5,):U(3,):R(5,)</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>Del(3,5):M2</t>
+          <t>Ins(2,):R(5,)</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>DEL:MH:3:2</t>
+          <t>INS:repeats:5+:5+</t>
         </is>
       </c>
       <c r="D54" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" s="4">
         <v>1</v>
@@ -5515,7 +5486,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>ATTTC</t>
+            <t>AGAAG</t>
           </r>
           <r>
             <rPr>
@@ -5526,19 +5497,10 @@
           <r>
             <rPr>
               <b/>
-              <u val="double"/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <b/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>G</t>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GAAAGAAA</t>
           </r>
           <r>
             <rPr>
@@ -5548,16 +5510,54 @@
           </r>
           <r>
             <rPr>
-              <u val="double"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAGTATCAAAACTGTCCACT</t>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GAAAGAAA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GAAAGAAA</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GAAAGAAA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GAAAGAAA</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GAAAGAAA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GAAAGAAA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GAAAAGAAAGAAAGAAAGAG</t>
           </r>
         </is>
       </c>
@@ -5565,24 +5565,24 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>Del3:M2</t>
+          <t>Del3:M1</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>Del(3,5):M2</t>
+          <t>Del(2,5):M1</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>DEL:MH:3:2</t>
+          <t>DEL:MH:3:1</t>
         </is>
       </c>
       <c r="D55" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TCCTC</t>
+            <t>TAGGT</t>
           </r>
           <r>
             <rPr>
@@ -5605,7 +5605,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>CT</t>
+            <t>G</t>
           </r>
           <r>
             <rPr>
@@ -5613,7 +5613,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>T</t>
+            <t>GA</t>
           </r>
           <r>
             <rPr>
@@ -5626,13 +5626,13 @@
               <u val="double"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>CT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AGTTCATTAATTGATCTTGG</t>
+            <t>G</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AAGTTTAAGTCAATGGATTA</t>
           </r>
         </is>
       </c>
@@ -5789,26 +5789,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="A16:A35"/>
-    <mergeCell ref="B16:B35"/>
-    <mergeCell ref="C16:C35"/>
-    <mergeCell ref="D16:D35"/>
-    <mergeCell ref="A37:A47"/>
-    <mergeCell ref="B37:B47"/>
-    <mergeCell ref="C37:C47"/>
-    <mergeCell ref="D37:D47"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="C48:C50"/>
-    <mergeCell ref="D48:D50"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="A2:A21"/>
+    <mergeCell ref="B2:B21"/>
+    <mergeCell ref="C2:C21"/>
+    <mergeCell ref="D2:D21"/>
+    <mergeCell ref="A22:A32"/>
+    <mergeCell ref="B22:B32"/>
+    <mergeCell ref="C22:C32"/>
+    <mergeCell ref="D22:D32"/>
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/development/one_file_rosetta_output/SP112959_rosetta.xlsx
+++ b/development/one_file_rosetta_output/SP112959_rosetta.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
@@ -4282,7 +4282,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TCTGA</t>
+            <t>AGAAA</t>
           </r>
           <r>
             <rPr>
@@ -4308,7 +4308,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AAAGCCAGAAAATAAGGGAA</t>
+            <t>AAAACTAATCCTTAGTGACT</t>
           </r>
         </is>
       </c>
@@ -4316,24 +4316,24 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Del(10,):U1:R1</t>
+          <t>A[Del(C):R1]A</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>Del(5,):R1</t>
+          <t>[Del(C):R1]A</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:5+:0</t>
+          <t>DEL:C:1:0</t>
         </is>
       </c>
       <c r="D37" s="4">
         <v>2</v>
       </c>
       <c r="E37" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TTTTG</t>
+            <t>TCTGA</t>
           </r>
           <r>
             <rPr>
@@ -4355,7 +4355,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AAAACTTTTTTCT</t>
+            <t>C</t>
           </r>
           <r>
             <rPr>
@@ -4367,7 +4367,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TCCCAGTACGTAGAGAAATC</t>
+            <t>AAAGCCAGAAAATAAGGGAA</t>
           </r>
         </is>
       </c>
@@ -4392,7 +4392,7 @@
         <v>2</v>
       </c>
       <c r="E38" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TTTTT</t>
+            <t>TTTTG</t>
           </r>
           <r>
             <rPr>
@@ -4414,7 +4414,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>CCTTTCAAAG</t>
+            <t>AAAACTTTTTTCT</t>
           </r>
           <r>
             <rPr>
@@ -4426,7 +4426,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AATATGCTTCCTACATGCTG</t>
+            <t>TCCCAGTACGTAGAGAAATC</t>
           </r>
         </is>
       </c>
@@ -4434,24 +4434,24 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Del3:M2</t>
+          <t>Del(10,):U1:R1</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>Del(3,5):M2</t>
+          <t>Del(5,):R1</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>DEL:MH:3:2</t>
+          <t>DEL:repeats:5+:0</t>
         </is>
       </c>
       <c r="D39" s="4">
         <v>2</v>
       </c>
       <c r="E39" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>ATTTC</t>
+            <t>TTTTT</t>
           </r>
           <r>
             <rPr>
@@ -4470,19 +4470,10 @@
           <r>
             <rPr>
               <b/>
-              <u val="double"/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <b/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>G</t>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CCTTTCAAAG</t>
           </r>
           <r>
             <rPr>
@@ -4492,16 +4483,9 @@
           </r>
           <r>
             <rPr>
-              <u val="double"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAGTATCAAAACTGTCCACT</t>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AATATGCTTCCTACATGCTG</t>
           </r>
         </is>
       </c>
@@ -4526,7 +4510,7 @@
         <v>2</v>
       </c>
       <c r="E40" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
@@ -4534,7 +4518,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TCCTC</t>
+            <t>ATTTC</t>
           </r>
           <r>
             <rPr>
@@ -4549,15 +4533,15 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>CT</t>
-          </r>
-          <r>
-            <rPr>
-              <b/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>G</t>
           </r>
           <r>
             <rPr>
@@ -4570,13 +4554,13 @@
               <u val="double"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>CT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AGTTCATTAATTGATCTTGG</t>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AAGTATCAAAACTGTCCACT</t>
           </r>
         </is>
       </c>
@@ -4584,30 +4568,74 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>A[Del(C):R2]T</t>
+          <t>Del3:M2</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>[Del(C):R2]T</t>
+          <t>Del(3,5):M2</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t/>
+          <t>DEL:MH:3:2</t>
         </is>
       </c>
       <c r="D41" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
           <r>
-            <rPr/>
-            <t/>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TCCTC</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>&lt;</t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <u val="double"/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CT</t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <u val="double"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AGTTCATTAATTGATCTTGG</t>
           </r>
         </is>
       </c>
@@ -4615,17 +4643,17 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>T[Del(C):R3]A</t>
+          <t>A[Del(C):R2]T</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>[Del(C):R3]A</t>
+          <t>[Del(C):R2]T</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>DEL:C:1:2</t>
+          <t>DEL:C:1:1</t>
         </is>
       </c>
       <c r="D42" s="4">
@@ -4640,7 +4668,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>GTTCT</t>
+            <t>CAAAA</t>
           </r>
           <r>
             <rPr>
@@ -4671,17 +4699,9 @@
           </r>
           <r>
             <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>C</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAAATTCAGTACTTCTGGC</t>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TTTTTACCTATAATAACAAA</t>
           </r>
         </is>
       </c>
@@ -4689,17 +4709,17 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>A[Del(T):R2]C</t>
+          <t>T[Del(C):R3]A</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>A[Del(T):R(1,4)]C</t>
+          <t>[Del(C):R3]A</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>DEL:T:1:1</t>
+          <t>DEL:C:1:2</t>
         </is>
       </c>
       <c r="D43" s="4">
@@ -4714,7 +4734,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TATGA</t>
+            <t>GTTCT</t>
           </r>
           <r>
             <rPr>
@@ -4728,7 +4748,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>T</t>
+            <t>C</t>
           </r>
           <r>
             <rPr>
@@ -4741,13 +4761,21 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>CTACACCTAGAAAACCCCAT</t>
+            <t>C</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>C</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AAAATTCAGTACTTCTGGC</t>
           </r>
         </is>
       </c>
@@ -4755,17 +4783,17 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>A[Del(T):R4]G</t>
+          <t>A[Del(T):R2]C</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>A[Del(T):R(1,4)]G</t>
+          <t>A[Del(T):R(1,4)]C</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t/>
+          <t>DEL:T:1:1</t>
         </is>
       </c>
       <c r="D44" s="4">
@@ -4777,8 +4805,43 @@
       <c r="F44" s="6" t="inlineStr">
         <is>
           <r>
-            <rPr/>
-            <t/>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>TATGA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>&lt;</t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CTACACCTAGAAAACCCCAT</t>
           </r>
         </is>
       </c>
@@ -4786,17 +4849,17 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>A[Del(T):R5]A</t>
+          <t>A[Del(T):R4]G</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>A[Del(T):R(5,7)]A</t>
+          <t>A[Del(T):R(1,4)]G</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>DEL:T:1:4</t>
+          <t>DEL:T:1:3</t>
         </is>
       </c>
       <c r="D45" s="4">
@@ -4811,7 +4874,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>ATTTA</t>
+            <t>TCCCA</t>
           </r>
           <r>
             <rPr>
@@ -4857,17 +4920,9 @@
           </r>
           <r>
             <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AGAGGTAAAAAATTCTT</t>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GTATGTTGCCTGTTCACTCT</t>
           </r>
         </is>
       </c>
@@ -4875,17 +4930,17 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>C[Del(T):R3]C</t>
+          <t>A[Del(T):R5]A</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>C[Del(T):R(1,4)]C</t>
+          <t>A[Del(T):R(5,7)]A</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t/>
+          <t>DEL:T:1:4</t>
         </is>
       </c>
       <c r="D46" s="4">
@@ -4897,8 +4952,66 @@
       <c r="F46" s="6" t="inlineStr">
         <is>
           <r>
-            <rPr/>
-            <t/>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>ATTTA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>&lt;</t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AGAGGTAAAAAATTCTT</t>
           </r>
         </is>
       </c>
@@ -4906,17 +5019,17 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>G[Del(T):R2]A</t>
+          <t>C[Del(T):R3]C</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>G[Del(T):R(1,4)]A</t>
+          <t>C[Del(T):R(1,4)]C</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>DEL:T:1:1</t>
+          <t>DEL:T:1:2</t>
         </is>
       </c>
       <c r="D47" s="4">
@@ -4931,7 +5044,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>CACAG</t>
+            <t>CGTTC</t>
           </r>
           <r>
             <rPr>
@@ -4962,9 +5075,17 @@
           </r>
           <r>
             <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AGGACAGGCTATTGGGGTTC</t>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CTATATTTGTGCTGAATCTA</t>
           </r>
         </is>
       </c>
@@ -4972,17 +5093,17 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>G[Del(T):R2]C</t>
+          <t>G[Del(T):R2]A</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>G[Del(T):R(1,4)]C</t>
+          <t>G[Del(T):R(1,4)]A</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t/>
+          <t>DEL:T:1:1</t>
         </is>
       </c>
       <c r="D48" s="4">
@@ -4994,8 +5115,43 @@
       <c r="F48" s="6" t="inlineStr">
         <is>
           <r>
-            <rPr/>
-            <t/>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CACAG</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>&lt;</t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AGGACAGGCTATTGGGGTTC</t>
           </r>
         </is>
       </c>
@@ -5003,17 +5159,17 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>A[Ins(T):R(9,)]C</t>
+          <t>G[Del(T):R2]C</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>A[Ins(T):R(8,)]C</t>
+          <t>G[Del(T):R(1,4)]C</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>INS:T:1:5+</t>
+          <t>DEL:T:1:1</t>
         </is>
       </c>
       <c r="D49" s="4">
@@ -5028,7 +5184,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TTTTA</t>
+            <t>TGCTG</t>
           </r>
           <r>
             <rPr>
@@ -5059,69 +5215,9 @@
           </r>
           <r>
             <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>CTTGCCTAACTG</t>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CCACTTGTTCCTAAATCCCT</t>
           </r>
         </is>
       </c>
@@ -5129,12 +5225,12 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>C[Ins(T):R(9,)]G</t>
+          <t>A[Ins(T):R(9,)]C</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>C[Ins(T):R(8,)]G</t>
+          <t>A[Ins(T):R(8,)]C</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -5154,7 +5250,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TTGGC</t>
+            <t>TTTTA</t>
           </r>
           <r>
             <rPr>
@@ -5247,7 +5343,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>GGAGACGGAGTT</t>
+            <t>CTTGCCTAACTG</t>
           </r>
         </is>
       </c>
@@ -5255,17 +5351,17 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>Del2:U2:R2</t>
+          <t>C[Ins(T):R(9,)]G</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>Del(2,8):U(1,2):R(2,4)</t>
+          <t>C[Ins(T):R(8,)]G</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:2:1</t>
+          <t>INS:T:1:5+</t>
         </is>
       </c>
       <c r="D51" s="4">
@@ -5280,7 +5376,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TGTAA</t>
+            <t>TTGGC</t>
           </r>
           <r>
             <rPr>
@@ -5294,7 +5390,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AC</t>
+            <t>T</t>
           </r>
           <r>
             <rPr>
@@ -5307,13 +5403,73 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AC</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AGTCAAAAGAGATTAAGTAT</t>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GGAGACGGAGTT</t>
           </r>
         </is>
       </c>
@@ -5321,17 +5477,17 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>Del3:U3:R3</t>
+          <t>Del2:U2:R2</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>Del(3,):U(3,):R(3,)</t>
+          <t>Del(2,8):U(1,2):R(2,4)</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>DEL:repeats:3:2</t>
+          <t>DEL:repeats:2:1</t>
         </is>
       </c>
       <c r="D52" s="4">
@@ -5346,7 +5502,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AGGAG</t>
+            <t>TGTAA</t>
           </r>
           <r>
             <rPr>
@@ -5360,7 +5516,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>ACC</t>
+            <t>AC</t>
           </r>
           <r>
             <rPr>
@@ -5373,21 +5529,13 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>ACC</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>ACC</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>ACTTTCACTCTAAATTAGCA</t>
+            <t>AC</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AGTCAAAAGAGATTAAGTAT</t>
           </r>
         </is>
       </c>
@@ -5395,17 +5543,17 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>Ins4:U2:R2</t>
+          <t>Del3:U3:R3</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>Ins(2,):R(2,4)</t>
+          <t>Del(3,):U(3,):R(3,)</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>INS:repeats:4:1</t>
+          <t>DEL:repeats:3:2</t>
         </is>
       </c>
       <c r="D53" s="4">
@@ -5420,7 +5568,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>ATGAT</t>
+            <t>AGGAG</t>
           </r>
           <r>
             <rPr>
@@ -5434,7 +5582,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TATA</t>
+            <t>ACC</t>
           </r>
           <r>
             <rPr>
@@ -5447,13 +5595,21 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TATA</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>CCACTGTACTCCAGCAGGGG</t>
+            <t>ACC</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>ACC</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>ACTTTCACTCTAAATTAGCA</t>
           </r>
         </is>
       </c>
@@ -5461,17 +5617,17 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>Ins(5,):U(3,):R(5,)</t>
+          <t>Ins4:U2:R2</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>Ins(2,):R(5,)</t>
+          <t>Ins(2,):R(2,4)</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>INS:repeats:5+:5+</t>
+          <t>INS:repeats:4:1</t>
         </is>
       </c>
       <c r="D54" s="4">
@@ -5486,7 +5642,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>AGAAG</t>
+            <t>ATGAT</t>
           </r>
           <r>
             <rPr>
@@ -5500,7 +5656,7 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>GAAAGAAA</t>
+            <t>TATA</t>
           </r>
           <r>
             <rPr>
@@ -5513,51 +5669,13 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>GAAAGAAA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GAAAGAAA</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GAAAGAAA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GAAAGAAA</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GAAAGAAA</t>
-          </r>
-          <r>
-            <rPr>
-              <u/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GAAAGAAA</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GAAAAGAAAGAAAGAAAGAG</t>
+            <t>TATA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>CCACTGTACTCCAGCAGGGG</t>
           </r>
         </is>
       </c>
@@ -5565,17 +5683,17 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>Del3:M1</t>
+          <t>Ins(5,):U(3,):R(5,)</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>Del(2,5):M1</t>
+          <t>Ins(2,):R(5,)</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>DEL:MH:3:1</t>
+          <t>INS:repeats:5+:5+</t>
         </is>
       </c>
       <c r="D55" s="4">
@@ -5590,7 +5708,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>TAGGT</t>
+            <t>AGAAG</t>
           </r>
           <r>
             <rPr>
@@ -5601,19 +5719,10 @@
           <r>
             <rPr>
               <b/>
-              <u val="double"/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>G</t>
-          </r>
-          <r>
-            <rPr>
-              <b/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GA</t>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GAAAGAAA</t>
           </r>
           <r>
             <rPr>
@@ -5623,16 +5732,54 @@
           </r>
           <r>
             <rPr>
-              <u val="double"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>G</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>AAGTTTAAGTCAATGGATTA</t>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GAAAGAAA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GAAAGAAA</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GAAAGAAA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GAAAGAAA</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GAAAGAAA</t>
+          </r>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GAAAGAAA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GAAAAGAAAGAAAGAAAGAG</t>
           </r>
         </is>
       </c>
@@ -5640,7 +5787,7 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>Del4:M1</t>
+          <t>Del3:M1</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
@@ -5650,7 +5797,7 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>DEL:MH:4:1</t>
+          <t>DEL:MH:3:1</t>
         </is>
       </c>
       <c r="D56" s="4">
@@ -5665,7 +5812,7 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>GTAAC</t>
+            <t>TAGGT</t>
           </r>
           <r>
             <rPr>
@@ -5680,15 +5827,15 @@
               <color rgb="FFFF1493"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <b/>
-              <color rgb="FFFF1493"/>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>ATT</t>
+            <t>G</t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GA</t>
           </r>
           <r>
             <rPr>
@@ -5701,13 +5848,13 @@
               <u val="double"/>
               <rFont val="Liberation Mono"/>
             </rPr>
-            <t>T</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Liberation Mono"/>
-            </rPr>
-            <t>GTTTGTTTTTCTGCTTCTAA</t>
+            <t>G</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>AAGTTTAAGTCAATGGATTA</t>
           </r>
         </is>
       </c>
@@ -5715,17 +5862,17 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>Del(7,):M3</t>
+          <t>Del4:M1</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>Del(6,):M3</t>
+          <t>Del(2,5):M1</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>DEL:MH:5+:3</t>
+          <t>DEL:MH:4:1</t>
         </is>
       </c>
       <c r="D57" s="4">
@@ -5740,6 +5887,81 @@
             <rPr>
               <rFont val="Liberation Mono"/>
             </rPr>
+            <t>GTAAC</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>&lt;</t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <u val="double"/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <color rgb="FFFF1493"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>ATT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <u val="double"/>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>T</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
+            <t>GTTTGTTTTTCTGCTTCTAA</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>Del(7,):M3</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>Del(6,):M3</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>DEL:MH:5+:3</t>
+        </is>
+      </c>
+      <c r="D58" s="4">
+        <v>1</v>
+      </c>
+      <c r="E58" s="4">
+        <v>1</v>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Liberation Mono"/>
+            </rPr>
             <t>GACGG</t>
           </r>
           <r>
@@ -5788,7 +6010,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="24">
     <mergeCell ref="A2:A21"/>
     <mergeCell ref="B2:B21"/>
     <mergeCell ref="C2:C21"/>
@@ -5801,14 +6023,18 @@
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="C33:C35"/>
     <mergeCell ref="D33:D35"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
